--- a/example/zh-CN/import/03_tiny_config.xlsx
+++ b/example/zh-CN/import/03_tiny_config.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -651,57 +651,57 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>活动倍率</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>activity_rate</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>活动倍率</t>
+          <t>公告</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>activity_rate</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>公告</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
           <t>notice</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>欢迎光临</t>
         </is>
